--- a/artfynd/A 40861-2025 artfynd.xlsx
+++ b/artfynd/A 40861-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>247884</v>
       </c>
       <c r="B2" t="n">
-        <v>104643</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691185.4807898523</v>
+        <v>691185</v>
       </c>
       <c r="R2" t="n">
-        <v>6620670.629513196</v>
+        <v>6620671</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>1994-08-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1994-08-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -791,6 +776,121 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Skogsstyrelsens naturvärdesobjekt</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6770707</v>
+      </c>
+      <c r="B3" t="n">
+        <v>107708</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>245</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skogsklocka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Campanula cervicaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Rö sn, S Rösjön, N Klövberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>691111</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6620759</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Rö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2002-06-10</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2002-06-10</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Svårdefinierad lokal</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Henry Gudmundson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Henry Gudmundson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Floraväkteri C-län</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 40861-2025 artfynd.xlsx
+++ b/artfynd/A 40861-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/247884</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,8 +903,17 @@
           <t>Floraväkteri C-län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6770707</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>